--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -662,6 +662,11 @@
           <t>NSE:VBL26SEP430PE</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2026-08-26 09:43:07</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -840,6 +845,11 @@
           <t>NSE:BSE26SEP3400PE</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2026-08-26 09:43:07</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1018,12 +1028,6 @@
           <t>NSE:PNB26SEP118CE</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -662,11 +662,6 @@
           <t>NSE:VBL26SEP430PE</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:43:07</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -845,11 +840,7 @@
           <t>NSE:BSE26SEP3400PE</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:43:07</t>
-        </is>
-      </c>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -751,6 +751,11 @@
           <t>NSE:GVT&amp;D26SEP4300PE</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-08-26 09:49:22</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -840,7 +845,6 @@
           <t>NSE:BSE26SEP3400PE</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -1023,6 +1023,11 @@
           <t>NSE:PNB26SEP118CE</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2026-08-26 09:50:56</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:AC7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1028,6 +1028,101 @@
           <t>2026-08-26 09:50:56</t>
         </is>
       </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-26 09:52:32</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SUZLON</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>47.39</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="H7" t="n">
+        <v>47</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N7" t="n">
+        <v>37593</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="S7" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>NSE:SUZLON26SEP47PE</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -751,11 +751,6 @@
           <t>NSE:GVT&amp;D26SEP4300PE</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:49:22</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1117,12 +1112,11 @@
           <t>NSE:SUZLON26SEP47PE</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-08-26 09:55:41</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -751,6 +751,11 @@
           <t>NSE:GVT&amp;D26SEP4300PE</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-08-26 09:57:15</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -840,6 +845,11 @@
           <t>NSE:BSE26SEP3400PE</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2026-08-26 09:57:15</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1016,11 +1026,6 @@
       <c r="W6" t="inlineStr">
         <is>
           <t>NSE:PNB26SEP118CE</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:50:56</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -845,11 +845,6 @@
           <t>NSE:BSE26SEP3400PE</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:57:15</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1026,6 +1021,11 @@
       <c r="W6" t="inlineStr">
         <is>
           <t>NSE:PNB26SEP118CE</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2026-08-26 10:00:23</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -751,11 +751,6 @@
           <t>NSE:GVT&amp;D26SEP4300PE</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:57:15</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -843,6 +838,11 @@
       <c r="W4" t="inlineStr">
         <is>
           <t>NSE:BSE26SEP3400PE</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2026-08-26 10:06:37</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -840,11 +840,7 @@
           <t>NSE:BSE26SEP3400PE</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2026-08-26 10:06:37</t>
-        </is>
-      </c>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -662,6 +662,11 @@
           <t>NSE:VBL26SEP430PE</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2026-08-26 10:09:43</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -840,7 +845,6 @@
           <t>NSE:BSE26SEP3400PE</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1122,6 +1122,101 @@
           <t>2026-08-26 09:55:41</t>
         </is>
       </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-26 10:15:59</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1530.1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1540</v>
+      </c>
+      <c r="I8" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>29.09</v>
+      </c>
+      <c r="K8" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="L8" t="n">
+        <v>47.33</v>
+      </c>
+      <c r="M8" t="n">
+        <v>52.69</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1366</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>0.845</v>
+      </c>
+      <c r="S8" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="T8" t="n">
+        <v>51.29</v>
+      </c>
+      <c r="U8" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NSE:UNITDSPR26SEP1540CE</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -662,11 +662,6 @@
           <t>NSE:VBL26SEP430PE</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2026-08-26 10:09:43</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1117,6 +1112,16 @@
           <t>NSE:SUZLON26SEP47PE</t>
         </is>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-26 10:17:34</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
           <t>2026-08-26 09:55:41</t>
@@ -1211,12 +1216,6 @@
           <t>NSE:UNITDSPR26SEP1540CE</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -751,6 +751,11 @@
           <t>NSE:GVT&amp;D26SEP4300PE</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-08-26 10:23:49</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -751,11 +751,6 @@
           <t>NSE:GVT&amp;D26SEP4300PE</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2026-08-26 10:23:49</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1219,6 +1214,11 @@
       <c r="W8" t="inlineStr">
         <is>
           <t>NSE:UNITDSPR26SEP1540CE</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-26 10:25:23</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -751,6 +751,11 @@
           <t>NSE:GVT&amp;D26SEP4300PE</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-08-26 10:26:56</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -751,11 +751,7 @@
           <t>NSE:GVT&amp;D26SEP4300PE</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2026-08-26 10:26:56</t>
-        </is>
-      </c>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -751,7 +751,6 @@
           <t>NSE:GVT&amp;D26SEP4300PE</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1217,11 +1216,7 @@
           <t>NSE:UNITDSPR26SEP1540CE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-08-26 10:25:23</t>
-        </is>
-      </c>
+      <c r="AC8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -751,6 +751,11 @@
           <t>NSE:GVT&amp;D26SEP4300PE</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-08-26 10:36:22</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1216,7 +1221,6 @@
           <t>NSE:UNITDSPR26SEP1540CE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -1221,6 +1221,11 @@
           <t>NSE:UNITDSPR26SEP1540CE</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-26 10:45:45</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -751,11 +751,7 @@
           <t>NSE:GVT&amp;D26SEP4300PE</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2026-08-26 10:36:22</t>
-        </is>
-      </c>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -751,7 +751,6 @@
           <t>NSE:GVT&amp;D26SEP4300PE</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1222,6 +1221,101 @@
           <t>2026-08-26 10:45:45</t>
         </is>
       </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-26 10:48:54</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>2271</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2280</v>
+      </c>
+      <c r="I9" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="J9" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="K9" t="n">
+        <v>82.73</v>
+      </c>
+      <c r="L9" t="n">
+        <v>90.13</v>
+      </c>
+      <c r="M9" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="N9" t="n">
+        <v>710</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="S9" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="T9" t="n">
+        <v>59.87</v>
+      </c>
+      <c r="U9" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>NSE:HYUNDAI26SEP2280CE</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -1310,12 +1310,11 @@
           <t>NSE:HYUNDAI26SEP2280CE</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-08-26 10:50:41</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -751,6 +751,11 @@
           <t>NSE:GVT&amp;D26SEP4300PE</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:00:05</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -845,6 +845,11 @@
           <t>NSE:BSE26SEP3400PE</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:01:41</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1219,11 +1224,6 @@
       <c r="W8" t="inlineStr">
         <is>
           <t>NSE:UNITDSPR26SEP1540CE</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-08-26 10:45:45</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -751,11 +751,6 @@
           <t>NSE:GVT&amp;D26SEP4300PE</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2026-08-26 11:00:05</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1224,6 +1219,11 @@
       <c r="W8" t="inlineStr">
         <is>
           <t>NSE:UNITDSPR26SEP1540CE</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:03:15</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -1221,11 +1221,7 @@
           <t>NSE:UNITDSPR26SEP1540CE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-08-26 11:03:15</t>
-        </is>
-      </c>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1313,11 +1309,6 @@
       <c r="W9" t="inlineStr">
         <is>
           <t>NSE:HYUNDAI26SEP2280CE</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2026-08-26 10:50:41</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -1221,7 +1221,6 @@
           <t>NSE:UNITDSPR26SEP1540CE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1309,6 +1308,11 @@
       <c r="W9" t="inlineStr">
         <is>
           <t>NSE:HYUNDAI26SEP2280CE</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:07:57</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -1221,6 +1221,11 @@
           <t>NSE:UNITDSPR26SEP1540CE</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:09:31</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1308,11 +1313,6 @@
       <c r="W9" t="inlineStr">
         <is>
           <t>NSE:HYUNDAI26SEP2280CE</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2026-08-26 11:07:57</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -1221,11 +1221,6 @@
           <t>NSE:UNITDSPR26SEP1540CE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-08-26 11:09:31</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1313,6 +1308,11 @@
       <c r="W9" t="inlineStr">
         <is>
           <t>NSE:HYUNDAI26SEP2280CE</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:11:05</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -1221,6 +1221,11 @@
           <t>NSE:UNITDSPR26SEP1540CE</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:14:15</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -1315,11 +1315,7 @@
           <t>NSE:HYUNDAI26SEP2280CE</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2026-08-26 11:11:05</t>
-        </is>
-      </c>
+      <c r="AC9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -1221,11 +1221,7 @@
           <t>NSE:UNITDSPR26SEP1540CE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-08-26 11:14:15</t>
-        </is>
-      </c>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1315,7 +1311,6 @@
           <t>NSE:HYUNDAI26SEP2280CE</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -662,6 +662,16 @@
           <t>NSE:VBL26SEP430PE</t>
         </is>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:17:39</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1221,7 +1231,6 @@
           <t>NSE:UNITDSPR26SEP1540CE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -1320,6 +1320,11 @@
           <t>NSE:HYUNDAI26SEP2280CE</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:25:15</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -1320,11 +1320,7 @@
           <t>NSE:HYUNDAI26SEP2280CE</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2026-08-26 11:25:15</t>
-        </is>
-      </c>
+      <c r="AC9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -1320,7 +1320,11 @@
           <t>NSE:HYUNDAI26SEP2280CE</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:28:23</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1325,6 +1325,101 @@
           <t>2026-08-26 11:28:23</t>
         </is>
       </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:58</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>INDUSTOWER</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>381.65</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="H10" t="n">
+        <v>381</v>
+      </c>
+      <c r="I10" t="n">
+        <v>8</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="K10" t="n">
+        <v>10</v>
+      </c>
+      <c r="L10" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="N10" t="n">
+        <v>6250</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>48.97</v>
+      </c>
+      <c r="U10" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Telecom</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>NSE:INDUSTOWER26SEP381PE</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -761,6 +761,11 @@
           <t>NSE:GVT&amp;D26SEP4300PE</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:33:07</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1414,12 +1419,6 @@
           <t>NSE:INDUSTOWER26SEP381PE</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -1419,6 +1419,11 @@
           <t>NSE:INDUSTOWER26SEP381PE</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:34:41</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1424,6 +1424,101 @@
           <t>2026-08-26 11:34:41</t>
         </is>
       </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:39:22</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BANDHANBNK</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>176.15</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="H11" t="n">
+        <v>175</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="M11" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="N11" t="n">
+        <v>10869</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="S11" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>52.97</v>
+      </c>
+      <c r="U11" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>NSE:BANDHANBNK26SEP175PE</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -1325,11 +1325,7 @@
           <t>NSE:HYUNDAI26SEP2280CE</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2026-08-26 11:28:23</t>
-        </is>
-      </c>
+      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1513,12 +1509,6 @@
           <t>NSE:BANDHANBNK26SEP175PE</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -1325,7 +1325,6 @@
           <t>NSE:HYUNDAI26SEP2280CE</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1507,6 +1506,11 @@
       <c r="W11" t="inlineStr">
         <is>
           <t>NSE:BANDHANBNK26SEP175PE</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:48:46</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -1414,11 +1414,7 @@
           <t>NSE:INDUSTOWER26SEP381PE</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2026-08-26 11:34:41</t>
-        </is>
-      </c>
+      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -1414,7 +1414,11 @@
           <t>NSE:INDUSTOWER26SEP381PE</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:56:37</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -1414,11 +1414,7 @@
           <t>NSE:INDUSTOWER26SEP381PE</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2026-08-26 11:56:37</t>
-        </is>
-      </c>
+      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -761,11 +761,6 @@
           <t>NSE:GVT&amp;D26SEP4300PE</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2026-08-26 11:33:07</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1325,6 +1320,11 @@
           <t>NSE:HYUNDAI26SEP2280CE</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-08-26 12:01:19</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1414,7 +1414,6 @@
           <t>NSE:INDUSTOWER26SEP381PE</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -761,6 +761,11 @@
           <t>NSE:GVT&amp;D26SEP4300PE</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-08-26 12:04:26</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -667,9 +667,14 @@
           <t>2026-08-26 11:17:39</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2026-08-26 12:08:09</t>
+        </is>
+      </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Target 1 Hit</t>
+          <t>Target 2 Hit</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -1241,6 +1241,11 @@
           <t>NSE:UNITDSPR26SEP1540CE</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-26 12:13:52</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -1518,6 +1518,16 @@
           <t>NSE:BANDHANBNK26SEP175PE</t>
         </is>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-26 12:21:39</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr">
         <is>
           <t>2026-08-26 11:48:46</t>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -1429,6 +1429,11 @@
           <t>NSE:INDUSTOWER26SEP381PE</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2026-08-26 13:05:32</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -1429,11 +1429,7 @@
           <t>NSE:INDUSTOWER26SEP381PE</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2026-08-26 13:05:32</t>
-        </is>
-      </c>
+      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -1429,7 +1429,11 @@
           <t>NSE:INDUSTOWER26SEP381PE</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2026-08-26 13:16:31</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1524,9 +1528,14 @@
           <t>2026-08-26 12:21:39</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>2026-08-26 13:16:32</t>
+        </is>
+      </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Target 1 Hit</t>
+          <t>Target 2 Hit</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1429,11 +1429,7 @@
           <t>NSE:INDUSTOWER26SEP381PE</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2026-08-26 13:16:31</t>
-        </is>
-      </c>
+      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1541,6 +1537,95 @@
       <c r="AC11" t="inlineStr">
         <is>
           <t>2026-08-26 11:48:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-26 13:18:08</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>KEI</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>5483.2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-1.88</v>
+      </c>
+      <c r="H12" t="n">
+        <v>5500</v>
+      </c>
+      <c r="I12" t="n">
+        <v>168.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>126.21</v>
+      </c>
+      <c r="K12" t="n">
+        <v>205.69</v>
+      </c>
+      <c r="L12" t="n">
+        <v>228.19</v>
+      </c>
+      <c r="M12" t="n">
+        <v>258.19</v>
+      </c>
+      <c r="N12" t="n">
+        <v>297</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>1.206</v>
+      </c>
+      <c r="S12" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>44.74</v>
+      </c>
+      <c r="U12" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>NSE:KEI26SEP5500CE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -1429,7 +1429,6 @@
           <t>NSE:INDUSTOWER26SEP381PE</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1626,6 +1625,11 @@
       <c r="W12" t="inlineStr">
         <is>
           <t>NSE:KEI26SEP5500CE</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2026-08-26 13:22:52</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -1429,6 +1429,11 @@
           <t>NSE:INDUSTOWER26SEP381PE</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2026-08-26 13:24:27</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1625,11 +1630,6 @@
       <c r="W12" t="inlineStr">
         <is>
           <t>NSE:KEI26SEP5500CE</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>2026-08-26 13:22:52</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -1043,6 +1043,16 @@
           <t>NSE:PNB26SEP118CE</t>
         </is>
       </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2026-08-26 13:27:09</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
           <t>2026-08-26 10:00:23</t>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -766,6 +766,16 @@
           <t>NSE:GVT&amp;D26SEP4300PE</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2026-08-26 13:40:39</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
           <t>2026-08-26 12:04:26</t>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -1652,6 +1652,11 @@
           <t>NSE:KEI26SEP5500CE</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2026-08-26 13:41:48</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1657,6 +1657,101 @@
           <t>2026-08-26 13:41:48</t>
         </is>
       </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-26 13:46:32</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GVT&amp;D</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>4313</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4300</v>
+      </c>
+      <c r="I13" t="n">
+        <v>152.1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>116.9</v>
+      </c>
+      <c r="K13" t="n">
+        <v>183.53</v>
+      </c>
+      <c r="L13" t="n">
+        <v>202.38</v>
+      </c>
+      <c r="M13" t="n">
+        <v>227.52</v>
+      </c>
+      <c r="N13" t="n">
+        <v>328</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="S13" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="T13" t="n">
+        <v>47.06</v>
+      </c>
+      <c r="U13" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>NSE:GVT&amp;D26SEP4300PE</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -672,9 +672,14 @@
           <t>2026-08-26 12:08:09</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2026-08-26 13:51:15</t>
+        </is>
+      </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Target 2 Hit</t>
+          <t>Target 3 Hit</t>
         </is>
       </c>
     </row>
@@ -1746,12 +1751,6 @@
           <t>NSE:GVT&amp;D26SEP4300PE</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC13"/>
+  <dimension ref="A1:AC14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1751,6 +1751,101 @@
           <t>NSE:GVT&amp;D26SEP4300PE</t>
         </is>
       </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-26 13:54:23</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DMART</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>3824</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-2.19</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3850</v>
+      </c>
+      <c r="I14" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>88.59</v>
+      </c>
+      <c r="K14" t="n">
+        <v>133.85</v>
+      </c>
+      <c r="L14" t="n">
+        <v>146.66</v>
+      </c>
+      <c r="M14" t="n">
+        <v>163.73</v>
+      </c>
+      <c r="N14" t="n">
+        <v>444</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="S14" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="T14" t="n">
+        <v>40.17</v>
+      </c>
+      <c r="U14" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>NSE:DMART26SEP3850PE</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC14"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1840,12 +1840,101 @@
           <t>NSE:DMART26SEP3850PE</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-26 13:55:58</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>INDUSTOWER</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>380.3</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-1.79</v>
+      </c>
+      <c r="H15" t="n">
+        <v>381</v>
+      </c>
+      <c r="I15" t="n">
+        <v>8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="K15" t="n">
+        <v>10</v>
+      </c>
+      <c r="L15" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="N15" t="n">
+        <v>6250</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="T15" t="n">
+        <v>48.16</v>
+      </c>
+      <c r="U15" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Telecom</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>NSE:INDUSTOWER26SEP381PE</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -1840,6 +1840,11 @@
           <t>NSE:DMART26SEP3850PE</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2026-08-26 13:57:33</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1929,12 +1934,6 @@
           <t>NSE:INDUSTOWER26SEP381PE</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -1751,6 +1751,11 @@
           <t>NSE:GVT&amp;D26SEP4300PE</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2026-08-26 14:02:18</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -1845,6 +1845,16 @@
           <t>NSE:DMART26SEP3850PE</t>
         </is>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-26 14:07:39</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
           <t>2026-08-26 13:57:33</t>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -1949,6 +1949,11 @@
           <t>NSE:INDUSTOWER26SEP381PE</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2026-08-26 14:13:14</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -1949,11 +1949,7 @@
           <t>NSE:INDUSTOWER26SEP381PE</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>2026-08-26 14:13:14</t>
-        </is>
-      </c>
+      <c r="AC15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -1949,7 +1949,11 @@
           <t>NSE:INDUSTOWER26SEP381PE</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2026-08-26 14:17:57</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -1949,11 +1949,7 @@
           <t>NSE:INDUSTOWER26SEP381PE</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>2026-08-26 14:17:57</t>
-        </is>
-      </c>
+      <c r="AC15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -1949,7 +1949,11 @@
           <t>NSE:INDUSTOWER26SEP381PE</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2026-08-26 14:30:31</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -969,6 +969,16 @@
           <t>NSE:LICHSGFIN26SEP520PE</t>
         </is>
       </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2026-08-26 14:36:09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -1370,6 +1370,16 @@
           <t>NSE:HYUNDAI26SEP2280CE</t>
         </is>
       </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2026-08-26 14:37:39</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
           <t>2026-08-26 12:01:19</t>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:AC16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1974,6 +1974,101 @@
           <t>2026-08-26 14:30:31</t>
         </is>
       </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-26 15:05:25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>INDUSTOWER</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>379.6</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-1.98</v>
+      </c>
+      <c r="H16" t="n">
+        <v>381</v>
+      </c>
+      <c r="I16" t="n">
+        <v>8</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="K16" t="n">
+        <v>10</v>
+      </c>
+      <c r="L16" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="N16" t="n">
+        <v>6250</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="n">
+        <v>47.75</v>
+      </c>
+      <c r="U16" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Telecom</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>NSE:INDUSTOWER26SEP381PE</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -2063,12 +2063,11 @@
           <t>NSE:INDUSTOWER26SEP381PE</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2026-08-26 15:08:35</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -2063,11 +2063,7 @@
           <t>NSE:INDUSTOWER26SEP381PE</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2026-08-26 15:08:35</t>
-        </is>
-      </c>
+      <c r="AC16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC16"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2063,7 +2063,101 @@
           <t>NSE:INDUSTOWER26SEP381PE</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-26 15:13:19</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1043.5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1040</v>
+      </c>
+      <c r="I17" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>28.13</v>
+      </c>
+      <c r="K17" t="n">
+        <v>45.87</v>
+      </c>
+      <c r="L17" t="n">
+        <v>50.89</v>
+      </c>
+      <c r="M17" t="n">
+        <v>57.59</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1333</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="S17" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="T17" t="n">
+        <v>88.79000000000001</v>
+      </c>
+      <c r="U17" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>NSE:MOTILALOFS26SEP1040CE</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -2063,6 +2063,11 @@
           <t>NSE:INDUSTOWER26SEP381PE</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2026-08-26 15:16:32</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2152,12 +2157,6 @@
           <t>NSE:MOTILALOFS26SEP1040CE</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -1677,6 +1677,16 @@
           <t>NSE:KEI26SEP5500CE</t>
         </is>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-26 15:25:09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
           <t>2026-08-26 13:41:48</t>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2073,11 +2073,6 @@
           <t>NSE:INDUSTOWER26SEP381PE</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2026-08-26 15:16:32</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2167,6 +2162,101 @@
           <t>NSE:MOTILALOFS26SEP1040CE</t>
         </is>
       </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-26 15:29:31</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PREMIERENE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1005</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-2.99</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I18" t="n">
+        <v>37</v>
+      </c>
+      <c r="J18" t="n">
+        <v>30.02</v>
+      </c>
+      <c r="K18" t="n">
+        <v>43.23</v>
+      </c>
+      <c r="L18" t="n">
+        <v>46.97</v>
+      </c>
+      <c r="M18" t="n">
+        <v>51.96</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1351</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R18" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="S18" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="T18" t="n">
+        <v>40.49</v>
+      </c>
+      <c r="U18" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>NSE:PREMIERENE26SEP1000PE</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
+++ b/backend/signal_logs/2026-08-26/signals_2026-08-26.xlsx
@@ -875,6 +875,11 @@
           <t>NSE:BSE26SEP3400PE</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Closed down ~143.2 (-1.0% from entry)</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr">
         <is>
           <t>2026-08-26 11:01:41</t>
@@ -1276,6 +1281,11 @@
           <t>NSE:UNITDSPR26SEP1540CE</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Closed down ~32.6 (-10.9% from entry)</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
           <t>2026-08-26 12:13:52</t>
@@ -1474,6 +1484,11 @@
           <t>NSE:INDUSTOWER26SEP381PE</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Closed up ~8.45 (+5.6% from entry)</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
           <t>2026-08-26 13:24:27</t>
@@ -1781,6 +1796,11 @@
           <t>NSE:GVT&amp;D26SEP4300PE</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Closed down ~133.05 (-12.5% from entry)</t>
+        </is>
+      </c>
       <c r="AC13" t="inlineStr">
         <is>
           <t>2026-08-26 14:02:18</t>
@@ -1979,6 +1999,11 @@
           <t>NSE:INDUSTOWER26SEP381PE</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>Closed up ~8.3 (+3.8% from entry)</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
           <t>2026-08-26 14:30:31</t>
@@ -2073,6 +2098,11 @@
           <t>NSE:INDUSTOWER26SEP381PE</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Closed up ~9.0 (+12.5% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2162,6 +2192,11 @@
           <t>NSE:MOTILALOFS26SEP1040CE</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>Closed down ~34.0 (-9.3% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2251,12 +2286,11 @@
           <t>NSE:PREMIERENE26SEP1000PE</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Closed up ~37.35 (+0.9% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
